--- a/products/gig-driver-mileage-tracker-2026.xlsx
+++ b/products/gig-driver-mileage-tracker-2026.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,8 +135,85 @@
       <color rgb="FFC9973A"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2D3068"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FFC98A3A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2D3068"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFC98A3A"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2D3068"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF5F6385"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF5F6385"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2D3068"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2D3068"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF5F6385"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF2D3068"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF5F6385"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFC98A3A"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -167,8 +244,26 @@
         <bgColor rgb="FFFAF8F4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF8EE"/>
+        <bgColor rgb="FFFBF8EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2D3068"/>
+        <bgColor rgb="FF2D3068"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ECE1"/>
+        <bgColor rgb="FFF0ECE1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -242,11 +337,39 @@
         <color rgb="FFE5E7ED"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC98A3A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC98A3A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC98A3A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC98A3A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF2D3068"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF2D3068"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF2D3068"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF2D3068"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -383,6 +506,114 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="27" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -785,10 +1016,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002D3068"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -801,23 +1033,25 @@
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="38" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="50" t="inlineStr">
         <is>
           <t>Gig Driver Mileage Tracker 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>SideHustleGuard · sidehustleguard.com</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="6" customHeight="1"/>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>What this tracker does</t>
         </is>
@@ -830,20 +1064,21 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>How to use it (3 steps)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="54" t="inlineStr">
         <is>
           <t>Open the Setup tab.</t>
         </is>
@@ -855,12 +1090,12 @@
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="54" t="inlineStr">
         <is>
           <t>Log trips on the Trip Log tab.</t>
         </is>
@@ -872,12 +1107,12 @@
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="53" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="54" t="inlineStr">
         <is>
           <t>Check the Monthly &amp; Year-End Summary tabs.</t>
         </is>
@@ -888,8 +1123,9 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="52" t="inlineStr">
         <is>
           <t>What the IRS actually requires</t>
         </is>
@@ -955,15 +1191,17 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="50" customHeight="1">
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t>This tracker captures all of the above. Save the file (or a print/PDF export) with your tax records for at least 3 years after filing — that's the standard IRS audit lookback window.</t>
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="50" customHeight="1">
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="56" t="inlineStr">
         <is>
           <t>Educational tool only — not tax or legal advice. The IRS standard mileage rate is set annually; verify the current year's rate at irs.gov/standardmileagerates before filing. For complex situations (employer reimbursements, multiple businesses, leased vehicles), consult a CPA.</t>
         </is>
@@ -995,10 +1233,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00E89464"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1009,22 +1248,24 @@
     <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="57" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>Edit the gold cells below. The rest of the tracker reads from here.</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>Tax year &amp; rate</t>
         </is>
@@ -1036,7 +1277,7 @@
           <t>Tax year</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="59" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1046,201 +1287,203 @@
           <t>IRS standard mileage rate ($/mile)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="60" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>← Verify at irs.gov/standardmileagerates each January. The IRS publishes the rate for the calendar year in mid-December.</t>
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="52" t="inlineStr">
         <is>
           <t>Your vehicles</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>Vehicle name</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>Year / Make / Model</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>Starting odometer (Jan 1)</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="61" t="inlineStr">
         <is>
           <t>Ending odometer (Dec 31)</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="61" t="inlineStr">
         <is>
           <t>Total miles (year)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>Main car</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="62" t="inlineStr">
         <is>
           <t>2020 Toyota Corolla</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="63" t="n">
         <v>38500</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="63" t="n">
         <v>78500</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="64">
         <f>IF(AND(ISNUMBER(D12),ISNUMBER(E12)),E12-D12,"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="62" t="inlineStr">
         <is>
           <t>Second car</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="17" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr"/>
-      <c r="F13" s="18">
+      <c r="C13" s="62" t="inlineStr"/>
+      <c r="D13" s="63" t="inlineStr"/>
+      <c r="E13" s="63" t="inlineStr"/>
+      <c r="F13" s="64">
         <f>IF(AND(ISNUMBER(D13),ISNUMBER(E13)),E13-D13,"")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>Backup / rental</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="17" t="inlineStr"/>
-      <c r="E14" s="17" t="inlineStr"/>
-      <c r="F14" s="18">
+      <c r="C14" s="62" t="inlineStr"/>
+      <c r="D14" s="63" t="inlineStr"/>
+      <c r="E14" s="63" t="inlineStr"/>
+      <c r="F14" s="64">
         <f>IF(AND(ISNUMBER(D14),ISNUMBER(E14)),E14-D14,"")</f>
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="24" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="52" t="inlineStr">
         <is>
           <t>Your gig platforms</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="58" t="inlineStr">
         <is>
           <t>Edit this list to match the apps you actually drive for.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t>DoorDash</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="62" t="inlineStr">
         <is>
           <t>Uber</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="62" t="inlineStr">
         <is>
           <t>Uber Eats</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="62" t="inlineStr">
         <is>
           <t>Lyft</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="62" t="inlineStr">
         <is>
           <t>Grubhub</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>Instacart</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="62" t="inlineStr">
         <is>
           <t>Amazon Flex</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>TaskRabbit</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="62" t="inlineStr">
         <is>
           <t>Rover</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>Shipt</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="62" t="inlineStr">
         <is>
           <t>Roadie</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="62" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1263,6 +1506,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00E89464"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1283,155 +1527,155 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>Trip Log — one row per business trip. Use dropdowns where they appear.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="66" t="inlineStr">
         <is>
           <t>Vehicle</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="66" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="66" t="inlineStr">
         <is>
           <t>Purpose / Route</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="66" t="inlineStr">
         <is>
           <t>Start odom.</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="F2" s="66" t="inlineStr">
         <is>
           <t>End odom.</t>
         </is>
       </c>
-      <c r="G2" s="20" t="inlineStr">
+      <c r="G2" s="66" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="H2" s="20" t="inlineStr">
+      <c r="H2" s="66" t="inlineStr">
         <is>
           <t>Business %</t>
         </is>
       </c>
-      <c r="I2" s="20" t="inlineStr">
+      <c r="I2" s="66" t="inlineStr">
         <is>
           <t>Business miles</t>
         </is>
       </c>
-      <c r="J2" s="20" t="inlineStr">
+      <c r="J2" s="66" t="inlineStr">
         <is>
           <t>Deduction $</t>
         </is>
       </c>
-      <c r="K2" s="20" t="inlineStr">
+      <c r="K2" s="66" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>2026-01-03</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="68" t="inlineStr">
         <is>
           <t>Main car</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="68" t="inlineStr">
         <is>
           <t>DoorDash</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="68" t="inlineStr">
         <is>
           <t>Long Beach lunch shift</t>
         </is>
       </c>
-      <c r="E3" s="23" t="n">
+      <c r="E3" s="69" t="n">
         <v>38500</v>
       </c>
-      <c r="F3" s="23" t="n">
+      <c r="F3" s="69" t="n">
         <v>38582</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="69">
         <f>IF(AND(ISNUMBER(E3),ISNUMBER(F3)),F3-E3,"")</f>
         <v/>
       </c>
-      <c r="H3" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="25">
+      <c r="H3" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="71">
         <f>IF(AND(ISNUMBER(G3),ISNUMBER(H3)),G3*H3,"")</f>
         <v/>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="72">
         <f>IF(ISNUMBER(I3),I3*MileRate,"")</f>
         <v/>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="68" t="inlineStr">
         <is>
           <t>First day driving — see formulas below for how miles/deduction auto-fill</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>2026-01-04</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="68" t="inlineStr">
         <is>
           <t>Main car</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="68" t="inlineStr">
         <is>
           <t>Uber</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="68" t="inlineStr">
         <is>
           <t>Friday airport runs</t>
         </is>
       </c>
-      <c r="E4" s="22" t="n"/>
-      <c r="F4" s="22" t="n"/>
-      <c r="G4" s="22" t="n">
+      <c r="E4" s="68" t="n"/>
+      <c r="F4" s="68" t="n"/>
+      <c r="G4" s="68" t="n">
         <v>73</v>
       </c>
-      <c r="H4" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="25">
+      <c r="H4" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="71">
         <f>IF(AND(ISNUMBER(G4),ISNUMBER(H4)),G4*H4,"")</f>
         <v/>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="72">
         <f>IF(ISNUMBER(I4),I4*MileRate,"")</f>
         <v/>
       </c>
-      <c r="K4" s="22" t="inlineStr">
+      <c r="K4" s="68" t="inlineStr">
         <is>
           <t>Used miles directly instead of odometer — both work</t>
         </is>
@@ -10220,10 +10464,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002D3068"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10234,42 +10479,44 @@
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="57" t="inlineStr">
         <is>
           <t>Monthly Summary</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>Pulled from the Trip Log automatically. Edit nothing here.</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="66" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="66" t="inlineStr">
         <is>
           <t>Trips</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>Total miles</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="66" t="inlineStr">
         <is>
           <t>Business miles</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="66" t="inlineStr">
         <is>
           <t>Deduction $</t>
         </is>
@@ -10552,52 +10799,54 @@
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="73">
         <f>SUM(C6:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="74">
         <f>SUM(D6:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="38">
+      <c r="E18" s="74">
         <f>SUM(E6:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="75">
         <f>SUM(F6:F17)</f>
         <v/>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="52" t="inlineStr">
         <is>
           <t>By platform (full year)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="66" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="66" t="inlineStr">
         <is>
           <t>Trips</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="66" t="inlineStr">
         <is>
           <t>Business miles</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="66" t="inlineStr">
         <is>
           <t>Deduction $</t>
         </is>
@@ -10832,10 +11081,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002D3068"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10848,63 +11098,67 @@
     <col width="2" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="57" t="inlineStr">
         <is>
           <t>Year-End Summary</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>What to put on Schedule C line 9 (Car &amp; Truck Expenses) when you file.</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>TAX YEAR</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="76" t="inlineStr">
         <is>
           <t>TOTAL BUSINESS MILES</t>
         </is>
       </c>
-      <c r="D5" s="40" t="inlineStr">
+      <c r="D5" s="76" t="inlineStr">
         <is>
           <t>IRS RATE</t>
         </is>
       </c>
-      <c r="E5" s="40" t="inlineStr">
+      <c r="E5" s="76" t="inlineStr">
         <is>
           <t>MILEAGE DEDUCTION</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="B6" s="41">
+      <c r="B6" s="77">
         <f>TaxYear</f>
         <v/>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="78">
         <f>'Monthly Summary'!E18</f>
         <v/>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="79">
         <f>MileRate</f>
         <v/>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="80">
         <f>'Monthly Summary'!F18</f>
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="10" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>Schedule C — Part II, Line 9 (Car &amp; Truck Expenses):</t>
         </is>
@@ -10916,8 +11170,10 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="52" t="inlineStr">
         <is>
           <t>Sanity check vs. your total driving</t>
         </is>
@@ -10929,7 +11185,7 @@
           <t>Total miles all vehicles drove this year (from Setup):</t>
         </is>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="82">
         <f>SUM(Setup!F12:F14)</f>
         <v/>
       </c>
@@ -10940,7 +11196,7 @@
           <t>Business miles you logged this year:</t>
         </is>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="83">
         <f>'Monthly Summary'!E18</f>
         <v/>
       </c>
@@ -10951,27 +11207,29 @@
           <t>Implied business-use percentage:</t>
         </is>
       </c>
-      <c r="C17" s="48">
+      <c r="C17" s="84">
         <f>IFERROR(C16/C15,"")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="50" customHeight="1">
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>If this percentage is above ~85%, expect IRS questions — most gig drivers fall in the 50–85% range because of commute, personal errands, and time between gigs. Reasonable numbers help you survive an audit.</t>
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="52" t="inlineStr">
         <is>
           <t>Records to keep with this file (3+ years)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="49" t="inlineStr">
+      <c r="B22" s="85" t="inlineStr">
         <is>
           <t>→</t>
         </is>
@@ -10983,7 +11241,7 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="49" t="inlineStr">
+      <c r="B23" s="85" t="inlineStr">
         <is>
           <t>→</t>
         </is>
@@ -10995,7 +11253,7 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="49" t="inlineStr">
+      <c r="B24" s="85" t="inlineStr">
         <is>
           <t>→</t>
         </is>
@@ -11007,7 +11265,7 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="49" t="inlineStr">
+      <c r="B25" s="85" t="inlineStr">
         <is>
           <t>→</t>
         </is>
@@ -11019,7 +11277,7 @@
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="49" t="inlineStr">
+      <c r="B26" s="85" t="inlineStr">
         <is>
           <t>→</t>
         </is>
@@ -11064,10 +11322,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002D3068"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C33"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -11075,27 +11334,29 @@
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="57" t="inlineStr">
         <is>
           <t>Plain-English IRS Reference</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>What every gig driver needs to know — short answers to the questions the IRS actually cares about.</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="81" t="inlineStr">
         <is>
           <t>Standard mileage vs. actual expenses</t>
         </is>
@@ -11108,13 +11369,14 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="81" t="inlineStr">
         <is>
           <t>Can I switch methods later?</t>
         </is>
@@ -11127,13 +11389,14 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C11" s="45" t="inlineStr">
+      <c r="C11" s="81" t="inlineStr">
         <is>
           <t>What counts as a business mile?</t>
         </is>
@@ -11146,13 +11409,14 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="49" t="inlineStr">
+      <c r="B14" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C14" s="81" t="inlineStr">
         <is>
           <t>Is my commute deductible?</t>
         </is>
@@ -11165,13 +11429,14 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C17" s="45" t="inlineStr">
+      <c r="C17" s="81" t="inlineStr">
         <is>
           <t>Do tolls and parking count?</t>
         </is>
@@ -11184,13 +11449,14 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="49" t="inlineStr">
+      <c r="B20" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C20" s="45" t="inlineStr">
+      <c r="C20" s="81" t="inlineStr">
         <is>
           <t>What about my phone, car wash, and hot bag?</t>
         </is>
@@ -11203,13 +11469,14 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="49" t="inlineStr">
+      <c r="B23" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C23" s="45" t="inlineStr">
+      <c r="C23" s="81" t="inlineStr">
         <is>
           <t>How long do I keep this log?</t>
         </is>
@@ -11222,13 +11489,14 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="49" t="inlineStr">
+      <c r="B26" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C26" s="45" t="inlineStr">
+      <c r="C26" s="81" t="inlineStr">
         <is>
           <t>What if I drove for two platforms at the same time?</t>
         </is>
@@ -11241,13 +11509,14 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="49" t="inlineStr">
+      <c r="B29" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C29" s="45" t="inlineStr">
+      <c r="C29" s="81" t="inlineStr">
         <is>
           <t>Do I need a paper log too?</t>
         </is>
@@ -11260,13 +11529,14 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="49" t="inlineStr">
+      <c r="B32" s="85" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C32" s="45" t="inlineStr">
+      <c r="C32" s="81" t="inlineStr">
         <is>
           <t>What if I forget to log a day?</t>
         </is>
